--- a/data/trans_orig/IP35_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP35_2023-Clase-trans_orig.xlsx
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>39477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57436</t>
+          <t>57274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>56781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82532</t>
+          <t>81327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103786</t>
+          <t>102482</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>132808</t>
+          <t>134047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33796</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37080</t>
+          <t>37034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43069</t>
+          <t>43695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65931</t>
+          <t>65806</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14071</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>30039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39326</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>839</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30042</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28463</t>
+          <t>28909</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>47131</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11133</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>21512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39329</t>
+          <t>39325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>17196</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30669</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30965</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>37210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58261</t>
+          <t>57582</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27479</t>
+          <t>26861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27580</t>
+          <t>27983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44814</t>
+          <t>45632</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>442</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3574,82 +3574,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>4624</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>15431</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>14694</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>9132</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>11,63%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>9115</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>4675</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>15637</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>14694</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>9137</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>21528</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19085</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>31273</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -5258,12 +5258,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5273,12 +5273,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>25624</t>
+          <t>26463</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>37948</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>437</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>17444</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>22952</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6505,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>39660</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>44668</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>44387</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>74848</t>
+          <t>75875</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>37414</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>47579</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>44278</t>
+          <t>43236</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>75858</t>
+          <t>78334</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>26085</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>42912</t>
+          <t>42944</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>63139</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>43910</t>
+          <t>43540</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>122569</t>
+          <t>122737</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>46457</t>
+          <t>46577</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>78869</t>
+          <t>77686</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>177610</t>
+          <t>169892</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>48661</t>
+          <t>49829</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>32122</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>61422</t>
+          <t>63295</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>98217</t>
+          <t>100576</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>40716</t>
+          <t>41066</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>60567</t>
+          <t>60225</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -7183,12 +7183,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -7752,12 +7752,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12366</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>391</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>397</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>17605</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>33381</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8430,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8500,12 +8500,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>27436</t>
+          <t>27431</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>33230</t>
+          <t>33276</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>69488</t>
+          <t>67875</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>54804</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>99095</t>
+          <t>97947</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -8656,12 +8656,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>34418</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>54147</t>
+          <t>52845</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>41598</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>68477</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>82591</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>114366</t>
+          <t>117288</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>26763</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>31899</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>27616</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>50752</t>
+          <t>50788</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>814</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -9903,12 +9903,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>34778</t>
+          <t>33342</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -10016,12 +10016,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -10129,12 +10129,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10214,12 +10214,12 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -10242,12 +10242,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>20268</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10277,12 +10277,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>21273</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>37086</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -10355,12 +10355,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>20932</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>39437</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>60365</t>
+          <t>60227</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -10468,12 +10468,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -10581,12 +10581,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>401</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10651,12 +10651,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>573</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -11037,12 +11037,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -11150,12 +11150,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>63818</t>
+          <t>64681</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>95967</t>
+          <t>95447</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11165,12 +11165,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>83620</t>
+          <t>84717</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>118938</t>
+          <t>121813</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>156637</t>
+          <t>156103</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>204499</t>
+          <t>203943</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -11263,12 +11263,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>41256</t>
+          <t>41281</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>65903</t>
+          <t>64750</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11278,12 +11278,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>45778</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>72668</t>
+          <t>71230</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>93835</t>
+          <t>92261</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>129921</t>
+          <t>129022</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -11376,12 +11376,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11391,12 +11391,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>22446</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11426,12 +11426,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>18366</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>35137</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -11539,12 +11539,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -11602,12 +11602,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>75804</t>
+          <t>76389</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>109277</t>
+          <t>110066</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11617,12 +11617,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>70092</t>
+          <t>68770</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>104554</t>
+          <t>104335</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -11652,12 +11652,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>155395</t>
+          <t>152451</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>201970</t>
+          <t>201071</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -11715,12 +11715,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>63730</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>96397</t>
+          <t>96218</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11750,12 +11750,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>57724</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>91626</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11765,12 +11765,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>130558</t>
+          <t>129307</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>174441</t>
+          <t>175147</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -11828,12 +11828,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>30464</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>51896</t>
+          <t>52152</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11863,12 +11863,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>55220</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>82675</t>
+          <t>83058</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11878,12 +11878,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>91383</t>
+          <t>90245</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>126843</t>
+          <t>126958</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>91726</t>
+          <t>92552</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>207834</t>
+          <t>198522</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>92720</t>
+          <t>94279</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>144727</t>
+          <t>150228</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12011,12 +12011,12 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>196646</t>
+          <t>197139</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>316374</t>
+          <t>333622</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -12054,12 +12054,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>99507</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>138238</t>
+          <t>137684</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>138565</t>
+          <t>137109</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>185791</t>
+          <t>185128</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>245521</t>
+          <t>246806</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>305682</t>
+          <t>311468</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -12167,12 +12167,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>34400</t>
+          <t>34644</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>70466</t>
+          <t>68580</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>72031</t>
+          <t>72009</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>84839</t>
+          <t>86244</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>129141</t>
+          <t>130690</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -12280,12 +12280,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12315,12 +12315,12 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -12330,12 +12330,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12350,12 +12350,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>31320</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -12398,7 +12398,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12428,12 +12428,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12443,12 +12443,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12463,12 +12463,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
